--- a/MASTER/cluster_plots_loadings/2019/pca_results_2019.xlsx
+++ b/MASTER/cluster_plots_loadings/2019/pca_results_2019.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,11 +444,6 @@
           <t>PC2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -462,9 +457,6 @@
       <c r="C2" t="n">
         <v>0.1535307299908061</v>
       </c>
-      <c r="D2" t="n">
-        <v>-0.5676686452681021</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -478,9 +470,6 @@
       <c r="C3" t="n">
         <v>0.05845944718084995</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.008048681854245671</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -494,9 +483,6 @@
       <c r="C4" t="n">
         <v>0.003227150553356647</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.00117302110643506</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -510,9 +496,6 @@
       <c r="C5" t="n">
         <v>0.4635603143086754</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.1275824217738802</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -526,9 +509,6 @@
       <c r="C6" t="n">
         <v>0.02923254325245667</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.006143450649366281</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -542,9 +522,6 @@
       <c r="C7" t="n">
         <v>0.583903979810443</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.2073074076550803</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -558,9 +535,6 @@
       <c r="C8" t="n">
         <v>0.4252007464878883</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.1126865728341357</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -574,9 +548,6 @@
       <c r="C9" t="n">
         <v>0.1318701982580227</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.003028939990674039</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -590,9 +561,6 @@
       <c r="C10" t="n">
         <v>0.02504285728790042</v>
       </c>
-      <c r="D10" t="n">
-        <v>0.01326391424001643</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -606,9 +574,6 @@
       <c r="C11" t="n">
         <v>0.02047863136685182</v>
       </c>
-      <c r="D11" t="n">
-        <v>0.001526815308945892</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -622,9 +587,6 @@
       <c r="C12" t="n">
         <v>-0.06210201144857764</v>
       </c>
-      <c r="D12" t="n">
-        <v>0.1462528358804941</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -638,9 +600,6 @@
       <c r="C13" t="n">
         <v>0.2840681410443012</v>
       </c>
-      <c r="D13" t="n">
-        <v>-0.4720993150076215</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -654,9 +613,6 @@
       <c r="C14" t="n">
         <v>-0.007131865635435758</v>
       </c>
-      <c r="D14" t="n">
-        <v>-0.02351854840456186</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -670,9 +626,6 @@
       <c r="C15" t="n">
         <v>0.07606138619130669</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.0140173086639672</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -686,9 +639,6 @@
       <c r="C16" t="n">
         <v>-0.02942175185363928</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.5956871997218083</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -702,9 +652,6 @@
       <c r="C17" t="n">
         <v>-0.00144655253236366</v>
       </c>
-      <c r="D17" t="n">
-        <v>-0.001760037014482793</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -718,9 +665,6 @@
       <c r="C18" t="n">
         <v>0.2525011308271665</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.047462505089485</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -734,9 +678,6 @@
       <c r="C19" t="n">
         <v>0.05001360809383606</v>
       </c>
-      <c r="D19" t="n">
-        <v>-0.04922412047043007</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -750,9 +691,6 @@
       <c r="C20" t="n">
         <v>0.02788820230067894</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.002079247067290826</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -765,9 +703,6 @@
       </c>
       <c r="C21" t="n">
         <v>0.2424678406815985</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.03107164187954296</v>
       </c>
     </row>
   </sheetData>
@@ -781,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,106 +730,83 @@
           <t>PC2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Natural Gas</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7596760432770628</v>
+        <v>0.546679397554517</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02942175185363928</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.5956871997218083</v>
+        <v>0.2840681410443012</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Natural Gas</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.546679397554517</v>
+        <v>0.7596760432770628</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2840681410443012</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-0.4720993150076215</v>
+        <v>-0.02942175185363928</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2547898039573664</v>
+        <v>-0.1037949525089634</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1535307299908061</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-0.5676686452681021</v>
+        <v>0.583903979810443</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1037949525089634</v>
+        <v>-0.2122643576428598</v>
       </c>
       <c r="C5" t="n">
-        <v>0.583903979810443</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.2073074076550803</v>
+        <v>0.4252007464878883</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Coal</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2122643576428598</v>
+        <v>-0.02693558592136593</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4252007464878883</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.1126865728341357</v>
+        <v>0.4635603143086754</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Coal</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.02693558592136593</v>
+        <v>0.2547898039573664</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4635603143086754</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.1275824217738802</v>
+        <v>0.1535307299908061</v>
       </c>
     </row>
     <row r="8">
@@ -909,9 +821,6 @@
       <c r="C8" t="n">
         <v>0.2525011308271665</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.047462505089485</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -925,40 +834,31 @@
       <c r="C9" t="n">
         <v>0.2424678406815985</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.03107164187954296</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.001533673588092213</v>
+        <v>-0.0005708128491523067</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.06210201144857764</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.1462528358804941</v>
+        <v>0.1318701982580227</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.0005708128491523067</v>
+        <v>0.01585567052320851</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1318701982580227</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.003028939990674039</v>
+        <v>0.07606138619130669</v>
       </c>
     </row>
     <row r="12">
@@ -973,24 +873,18 @@
       <c r="C12" t="n">
         <v>0.05001360809383606</v>
       </c>
-      <c r="D12" t="n">
-        <v>-0.04922412047043007</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01585567052320851</v>
+        <v>-0.001533673588092213</v>
       </c>
       <c r="C13" t="n">
-        <v>0.07606138619130669</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0140173086639672</v>
+        <v>-0.06210201144857764</v>
       </c>
     </row>
     <row r="14">
@@ -1005,9 +899,6 @@
       <c r="C14" t="n">
         <v>0.05845944718084995</v>
       </c>
-      <c r="D14" t="n">
-        <v>0.008048681854245671</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1021,9 +912,6 @@
       <c r="C15" t="n">
         <v>0.02923254325245667</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.006143450649366281</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1037,9 +925,6 @@
       <c r="C16" t="n">
         <v>0.02504285728790042</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.01326391424001643</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1053,40 +938,31 @@
       <c r="C17" t="n">
         <v>0.02788820230067894</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.002079247067290826</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Natural Graphite</t>
+          <t>Magnesium compounds</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.007111184779207292</v>
+        <v>0.00617903378996942</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.007131865635435758</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-0.02351854840456186</v>
+        <v>0.02047863136685182</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Magnesium compounds</t>
+          <t>Natural Graphite</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.00617903378996942</v>
+        <v>-0.007111184779207292</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02047863136685182</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.001526815308945892</v>
+        <v>-0.007131865635435758</v>
       </c>
     </row>
     <row r="20">
@@ -1101,9 +977,6 @@
       <c r="C20" t="n">
         <v>0.003227150553356647</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.00117302110643506</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1116,9 +989,6 @@
       </c>
       <c r="C21" t="n">
         <v>-0.00144655253236366</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-0.001760037014482793</v>
       </c>
     </row>
   </sheetData>
@@ -1132,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1151,11 +1021,6 @@
           <t>PC2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1164,13 +1029,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-3.604437349367783</v>
+        <v>-0.8826882968525365</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.8262183412441408</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.6235250867440436</v>
+        <v>5.092806443088156</v>
       </c>
     </row>
     <row r="3">
@@ -1180,13 +1042,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.715776811016249</v>
+        <v>-3.604437349367783</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.807003205444063</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.746198562221021</v>
+        <v>-0.8262183412441408</v>
       </c>
     </row>
     <row r="4">
@@ -1196,13 +1055,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.823093592518211</v>
+        <v>1.756538917031794</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08412669394896914</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-1.260487309513375</v>
+        <v>-1.656040393765002</v>
       </c>
     </row>
     <row r="5">
@@ -1212,13 +1068,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.8826882968525365</v>
+        <v>6.176758322246646</v>
       </c>
       <c r="C5" t="n">
-        <v>5.092806443088156</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.6102913755178533</v>
+        <v>0.06189174753758728</v>
       </c>
     </row>
   </sheetData>
@@ -1232,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1251,11 +1104,6 @@
           <t>PC2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1264,13 +1112,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6614895523195116</v>
+        <v>3.815065695433516</v>
       </c>
       <c r="C2" t="n">
-        <v>1.367024097762203</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.6983478304506834</v>
+        <v>2.031042890142356</v>
       </c>
     </row>
     <row r="3">
@@ -1280,13 +1125,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.380141831156451</v>
+        <v>0.6614895523195116</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9417967463077646</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.459747722672819</v>
+        <v>1.367024097762203</v>
       </c>
     </row>
     <row r="4">
@@ -1296,13 +1138,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.052181238224621</v>
+        <v>1.334739953338542</v>
       </c>
       <c r="C4" t="n">
-        <v>1.119700998990653</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.700403302225601</v>
+        <v>1.066681106159855</v>
       </c>
     </row>
     <row r="5">
@@ -1312,13 +1151,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.815065695433516</v>
+        <v>1.77500600403629</v>
       </c>
       <c r="C5" t="n">
-        <v>2.031042890142356</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.30011266852303</v>
+        <v>1.177705870599266</v>
       </c>
     </row>
   </sheetData>
@@ -1354,7 +1190,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1364,7 +1200,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -1374,7 +1210,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -1384,7 +1220,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1398,7 +1234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1430,7 +1266,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-3.604437349367783</v>
+        <v>-0.8826882968525365</v>
       </c>
     </row>
     <row r="3">
@@ -1445,7 +1281,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.715776811016249</v>
+        <v>-3.604437349367783</v>
       </c>
     </row>
     <row r="4">
@@ -1460,7 +1296,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.823093592518211</v>
+        <v>1.756538917031794</v>
       </c>
     </row>
     <row r="5">
@@ -1475,7 +1311,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.8826882968525365</v>
+        <v>6.176758322246646</v>
       </c>
     </row>
     <row r="6">
@@ -1490,7 +1326,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.8262183412441408</v>
+        <v>5.092806443088156</v>
       </c>
     </row>
     <row r="7">
@@ -1505,7 +1341,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-1.807003205444063</v>
+        <v>-0.8262183412441408</v>
       </c>
     </row>
     <row r="8">
@@ -1520,7 +1356,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.08412669394896914</v>
+        <v>-1.656040393765002</v>
       </c>
     </row>
     <row r="9">
@@ -1535,67 +1371,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.092806443088156</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.6235250867440436</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1.746198562221021</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>-1.260487309513375</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.6102913755178533</v>
+        <v>0.06189174753758728</v>
       </c>
     </row>
   </sheetData>
